--- a/data_cache/excel/KESORAMIND_historical.xlsx
+++ b/data_cache/excel/KESORAMIND_historical.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:G252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,15 +429,25 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>traded_quantity</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>delivery_quantity</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>delivery_pct</t>
         </is>
@@ -446,1216 +456,6275 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.09</v>
+        <v>208.54</v>
       </c>
       <c r="C2" t="n">
-        <v>876500</v>
+        <v>208.54</v>
       </c>
       <c r="D2" t="n">
-        <v>753454</v>
+        <v>208.54</v>
       </c>
       <c r="E2" t="n">
-        <v>85.95999999999999</v>
+        <v>234879</v>
+      </c>
+      <c r="F2" t="n">
+        <v>157116</v>
+      </c>
+      <c r="G2" t="n">
+        <v>66.89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.16</v>
+        <v>209.17</v>
       </c>
       <c r="C3" t="n">
-        <v>687607</v>
+        <v>209.17</v>
       </c>
       <c r="D3" t="n">
-        <v>560861</v>
+        <v>209.17</v>
       </c>
       <c r="E3" t="n">
-        <v>81.56999999999999</v>
+        <v>272869</v>
+      </c>
+      <c r="F3" t="n">
+        <v>154927</v>
+      </c>
+      <c r="G3" t="n">
+        <v>56.78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.1</v>
+        <v>206.78</v>
       </c>
       <c r="C4" t="n">
-        <v>575953</v>
+        <v>206.78</v>
       </c>
       <c r="D4" t="n">
-        <v>403280</v>
+        <v>206.78</v>
       </c>
       <c r="E4" t="n">
-        <v>70.02</v>
+        <v>260390</v>
+      </c>
+      <c r="F4" t="n">
+        <v>146710</v>
+      </c>
+      <c r="G4" t="n">
+        <v>56.34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.06</v>
+        <v>208.37</v>
       </c>
       <c r="C5" t="n">
-        <v>549930</v>
+        <v>208.37</v>
       </c>
       <c r="D5" t="n">
-        <v>378261</v>
+        <v>208.37</v>
       </c>
       <c r="E5" t="n">
-        <v>68.78</v>
+        <v>106572</v>
+      </c>
+      <c r="F5" t="n">
+        <v>52083</v>
+      </c>
+      <c r="G5" t="n">
+        <v>48.87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.06</v>
+        <v>209.67</v>
       </c>
       <c r="C6" t="n">
-        <v>851170</v>
+        <v>209.67</v>
       </c>
       <c r="D6" t="n">
-        <v>584958</v>
+        <v>209.67</v>
       </c>
       <c r="E6" t="n">
-        <v>68.72</v>
+        <v>378787</v>
+      </c>
+      <c r="F6" t="n">
+        <v>218506</v>
+      </c>
+      <c r="G6" t="n">
+        <v>57.69</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.06</v>
+        <v>210.33</v>
       </c>
       <c r="C7" t="n">
-        <v>334425</v>
+        <v>210.33</v>
       </c>
       <c r="D7" t="n">
-        <v>254436</v>
+        <v>210.33</v>
       </c>
       <c r="E7" t="n">
-        <v>76.08</v>
+        <v>235734</v>
+      </c>
+      <c r="F7" t="n">
+        <v>170308</v>
+      </c>
+      <c r="G7" t="n">
+        <v>72.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.03</v>
+        <v>209.74</v>
       </c>
       <c r="C8" t="n">
-        <v>515753</v>
+        <v>209.74</v>
       </c>
       <c r="D8" t="n">
-        <v>324387</v>
+        <v>209.74</v>
       </c>
       <c r="E8" t="n">
-        <v>62.9</v>
+        <v>234090</v>
+      </c>
+      <c r="F8" t="n">
+        <v>108381</v>
+      </c>
+      <c r="G8" t="n">
+        <v>46.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.97</v>
+        <v>207.03</v>
       </c>
       <c r="C9" t="n">
-        <v>717814</v>
+        <v>207.03</v>
       </c>
       <c r="D9" t="n">
-        <v>498709</v>
+        <v>207.03</v>
       </c>
       <c r="E9" t="n">
-        <v>69.48</v>
+        <v>3390945</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3020107</v>
+      </c>
+      <c r="G9" t="n">
+        <v>89.06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>206.86</v>
       </c>
       <c r="C10" t="n">
-        <v>505067</v>
+        <v>206.86</v>
       </c>
       <c r="D10" t="n">
-        <v>375941</v>
+        <v>206.86</v>
       </c>
       <c r="E10" t="n">
-        <v>74.43000000000001</v>
+        <v>1387640</v>
+      </c>
+      <c r="F10" t="n">
+        <v>993935</v>
+      </c>
+      <c r="G10" t="n">
+        <v>71.63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.94</v>
+        <v>208.85</v>
       </c>
       <c r="C11" t="n">
-        <v>558714</v>
+        <v>208.85</v>
       </c>
       <c r="D11" t="n">
-        <v>395397</v>
+        <v>208.85</v>
       </c>
       <c r="E11" t="n">
-        <v>70.77</v>
+        <v>4685695</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3906131</v>
+      </c>
+      <c r="G11" t="n">
+        <v>83.36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.86</v>
+        <v>210.63</v>
       </c>
       <c r="C12" t="n">
-        <v>474312</v>
+        <v>210.63</v>
       </c>
       <c r="D12" t="n">
-        <v>376199</v>
+        <v>210.63</v>
       </c>
       <c r="E12" t="n">
-        <v>79.31</v>
+        <v>349741</v>
+      </c>
+      <c r="F12" t="n">
+        <v>162634</v>
+      </c>
+      <c r="G12" t="n">
+        <v>46.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.69</v>
+        <v>212</v>
       </c>
       <c r="C13" t="n">
-        <v>585617</v>
+        <v>212</v>
       </c>
       <c r="D13" t="n">
-        <v>353238</v>
+        <v>212</v>
       </c>
       <c r="E13" t="n">
-        <v>60.32</v>
+        <v>289638</v>
+      </c>
+      <c r="F13" t="n">
+        <v>149849</v>
+      </c>
+      <c r="G13" t="n">
+        <v>51.74</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.15</v>
+        <v>214.12</v>
       </c>
       <c r="C14" t="n">
-        <v>1116479</v>
+        <v>214.12</v>
       </c>
       <c r="D14" t="n">
-        <v>852650</v>
+        <v>214.12</v>
       </c>
       <c r="E14" t="n">
-        <v>76.37</v>
+        <v>415363</v>
+      </c>
+      <c r="F14" t="n">
+        <v>188170</v>
+      </c>
+      <c r="G14" t="n">
+        <v>45.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.3</v>
+        <v>213.99</v>
       </c>
       <c r="C15" t="n">
-        <v>6680188</v>
+        <v>213.99</v>
       </c>
       <c r="D15" t="n">
-        <v>3446692</v>
+        <v>213.99</v>
       </c>
       <c r="E15" t="n">
-        <v>51.6</v>
+        <v>817227</v>
+      </c>
+      <c r="F15" t="n">
+        <v>407672</v>
+      </c>
+      <c r="G15" t="n">
+        <v>49.88</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.07</v>
+        <v>211.77</v>
       </c>
       <c r="C16" t="n">
-        <v>940780</v>
+        <v>211.77</v>
       </c>
       <c r="D16" t="n">
-        <v>655323</v>
+        <v>211.77</v>
       </c>
       <c r="E16" t="n">
-        <v>69.66</v>
+        <v>277789</v>
+      </c>
+      <c r="F16" t="n">
+        <v>167741</v>
+      </c>
+      <c r="G16" t="n">
+        <v>60.38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.24</v>
+        <v>214.02</v>
       </c>
       <c r="C17" t="n">
-        <v>796020</v>
+        <v>214.02</v>
       </c>
       <c r="D17" t="n">
-        <v>419572</v>
+        <v>214.02</v>
       </c>
       <c r="E17" t="n">
-        <v>52.71</v>
+        <v>557137</v>
+      </c>
+      <c r="F17" t="n">
+        <v>319521</v>
+      </c>
+      <c r="G17" t="n">
+        <v>57.35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.21</v>
+        <v>216.99</v>
       </c>
       <c r="C18" t="n">
-        <v>431146</v>
+        <v>216.99</v>
       </c>
       <c r="D18" t="n">
-        <v>268399</v>
+        <v>216.99</v>
       </c>
       <c r="E18" t="n">
-        <v>62.25</v>
+        <v>1604479</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1148056</v>
+      </c>
+      <c r="G18" t="n">
+        <v>71.55</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.31</v>
+        <v>214.77</v>
       </c>
       <c r="C19" t="n">
-        <v>775798</v>
+        <v>214.77</v>
       </c>
       <c r="D19" t="n">
-        <v>400084</v>
+        <v>214.77</v>
       </c>
       <c r="E19" t="n">
-        <v>51.57</v>
+        <v>272017</v>
+      </c>
+      <c r="F19" t="n">
+        <v>126040</v>
+      </c>
+      <c r="G19" t="n">
+        <v>46.34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.48</v>
+        <v>219.1</v>
       </c>
       <c r="C20" t="n">
-        <v>3152788</v>
+        <v>219.1</v>
       </c>
       <c r="D20" t="n">
-        <v>1292585</v>
+        <v>219.1</v>
       </c>
       <c r="E20" t="n">
-        <v>41</v>
+        <v>425169</v>
+      </c>
+      <c r="F20" t="n">
+        <v>215946</v>
+      </c>
+      <c r="G20" t="n">
+        <v>50.79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.47</v>
+        <v>219.5</v>
       </c>
       <c r="C21" t="n">
-        <v>2403923</v>
+        <v>219.5</v>
       </c>
       <c r="D21" t="n">
-        <v>1421706</v>
+        <v>219.5</v>
       </c>
       <c r="E21" t="n">
-        <v>59.14</v>
+        <v>408273</v>
+      </c>
+      <c r="F21" t="n">
+        <v>186621</v>
+      </c>
+      <c r="G21" t="n">
+        <v>45.71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.4</v>
+        <v>219.42</v>
       </c>
       <c r="C22" t="n">
-        <v>650061</v>
+        <v>219.42</v>
       </c>
       <c r="D22" t="n">
-        <v>436274</v>
+        <v>219.42</v>
       </c>
       <c r="E22" t="n">
-        <v>67.11</v>
+        <v>452366</v>
+      </c>
+      <c r="F22" t="n">
+        <v>279382</v>
+      </c>
+      <c r="G22" t="n">
+        <v>61.76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5.35</v>
+        <v>218.73</v>
       </c>
       <c r="C23" t="n">
-        <v>410522</v>
+        <v>218.73</v>
       </c>
       <c r="D23" t="n">
-        <v>301427</v>
+        <v>218.73</v>
       </c>
       <c r="E23" t="n">
-        <v>73.43000000000001</v>
+        <v>498263</v>
+      </c>
+      <c r="F23" t="n">
+        <v>284760</v>
+      </c>
+      <c r="G23" t="n">
+        <v>57.15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5.45</v>
+        <v>217.74</v>
       </c>
       <c r="C24" t="n">
-        <v>1265186</v>
+        <v>217.74</v>
       </c>
       <c r="D24" t="n">
-        <v>943476</v>
+        <v>217.74</v>
       </c>
       <c r="E24" t="n">
-        <v>74.56999999999999</v>
+        <v>807390</v>
+      </c>
+      <c r="F24" t="n">
+        <v>501239</v>
+      </c>
+      <c r="G24" t="n">
+        <v>62.08</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.54</v>
+        <v>217.95</v>
       </c>
       <c r="C25" t="n">
-        <v>27546759</v>
+        <v>217.95</v>
       </c>
       <c r="D25" t="n">
-        <v>17622370</v>
+        <v>217.95</v>
       </c>
       <c r="E25" t="n">
-        <v>63.97</v>
+        <v>461704</v>
+      </c>
+      <c r="F25" t="n">
+        <v>211379</v>
+      </c>
+      <c r="G25" t="n">
+        <v>45.78</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7.84</v>
+        <v>221.74</v>
       </c>
       <c r="C26" t="n">
-        <v>23271133</v>
+        <v>221.74</v>
       </c>
       <c r="D26" t="n">
-        <v>10720183</v>
+        <v>221.74</v>
       </c>
       <c r="E26" t="n">
-        <v>46.07</v>
+        <v>585561</v>
+      </c>
+      <c r="F26" t="n">
+        <v>256063</v>
+      </c>
+      <c r="G26" t="n">
+        <v>43.73</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.93</v>
+        <v>225.95</v>
       </c>
       <c r="C27" t="n">
-        <v>33227088</v>
+        <v>225.95</v>
       </c>
       <c r="D27" t="n">
-        <v>13115294</v>
+        <v>225.95</v>
       </c>
       <c r="E27" t="n">
-        <v>39.47</v>
+        <v>931249</v>
+      </c>
+      <c r="F27" t="n">
+        <v>390722</v>
+      </c>
+      <c r="G27" t="n">
+        <v>41.96</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8.08</v>
+        <v>222.01</v>
       </c>
       <c r="C28" t="n">
-        <v>17988293</v>
+        <v>222.01</v>
       </c>
       <c r="D28" t="n">
-        <v>6384582</v>
+        <v>222.01</v>
       </c>
       <c r="E28" t="n">
-        <v>35.49</v>
+        <v>312315</v>
+      </c>
+      <c r="F28" t="n">
+        <v>150584</v>
+      </c>
+      <c r="G28" t="n">
+        <v>48.22</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7.8</v>
+        <v>223.16</v>
       </c>
       <c r="C29" t="n">
-        <v>6419042</v>
+        <v>223.16</v>
       </c>
       <c r="D29" t="n">
-        <v>3405087</v>
+        <v>223.16</v>
       </c>
       <c r="E29" t="n">
-        <v>53.05</v>
+        <v>252557</v>
+      </c>
+      <c r="F29" t="n">
+        <v>119060</v>
+      </c>
+      <c r="G29" t="n">
+        <v>47.14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7.81</v>
+        <v>228.31</v>
       </c>
       <c r="C30" t="n">
-        <v>1241894</v>
+        <v>228.31</v>
       </c>
       <c r="D30" t="n">
-        <v>763984</v>
+        <v>228.31</v>
       </c>
       <c r="E30" t="n">
-        <v>61.52</v>
+        <v>329207</v>
+      </c>
+      <c r="F30" t="n">
+        <v>164427</v>
+      </c>
+      <c r="G30" t="n">
+        <v>49.95</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>8.59</v>
+        <v>225.8</v>
       </c>
       <c r="C31" t="n">
-        <v>1297041</v>
+        <v>225.8</v>
       </c>
       <c r="D31" t="n">
-        <v>885426</v>
+        <v>225.8</v>
       </c>
       <c r="E31" t="n">
-        <v>68.27</v>
+        <v>732023</v>
+      </c>
+      <c r="F31" t="n">
+        <v>405085</v>
+      </c>
+      <c r="G31" t="n">
+        <v>55.34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>9.1</v>
+        <v>223.99</v>
       </c>
       <c r="C32" t="n">
-        <v>2443810</v>
+        <v>223.99</v>
       </c>
       <c r="D32" t="n">
-        <v>1548415</v>
+        <v>223.99</v>
       </c>
       <c r="E32" t="n">
-        <v>63.36</v>
+        <v>465745</v>
+      </c>
+      <c r="F32" t="n">
+        <v>217460</v>
+      </c>
+      <c r="G32" t="n">
+        <v>46.69</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>9.1</v>
+        <v>224.31</v>
       </c>
       <c r="C33" t="n">
-        <v>2443810</v>
+        <v>224.31</v>
       </c>
       <c r="D33" t="n">
-        <v>1548415</v>
+        <v>224.31</v>
       </c>
       <c r="E33" t="n">
-        <v>63.36</v>
+        <v>508646</v>
+      </c>
+      <c r="F33" t="n">
+        <v>213298</v>
+      </c>
+      <c r="G33" t="n">
+        <v>41.93</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>8.539999999999999</v>
+        <v>224.31</v>
       </c>
       <c r="C34" t="n">
-        <v>1538645</v>
+        <v>224.31</v>
       </c>
       <c r="D34" t="n">
-        <v>1178198</v>
+        <v>224.31</v>
       </c>
       <c r="E34" t="n">
-        <v>76.56999999999999</v>
+        <v>508646</v>
+      </c>
+      <c r="F34" t="n">
+        <v>213298</v>
+      </c>
+      <c r="G34" t="n">
+        <v>41.93</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>8.07</v>
+        <v>222.94</v>
       </c>
       <c r="C35" t="n">
-        <v>1694201</v>
+        <v>222.94</v>
       </c>
       <c r="D35" t="n">
-        <v>1117022</v>
+        <v>222.94</v>
       </c>
       <c r="E35" t="n">
-        <v>65.93000000000001</v>
+        <v>290200</v>
+      </c>
+      <c r="F35" t="n">
+        <v>127955</v>
+      </c>
+      <c r="G35" t="n">
+        <v>44.09</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>8.32</v>
+        <v>217.05</v>
       </c>
       <c r="C36" t="n">
-        <v>1015707</v>
+        <v>217.05</v>
       </c>
       <c r="D36" t="n">
-        <v>624448</v>
+        <v>217.05</v>
       </c>
       <c r="E36" t="n">
-        <v>61.48</v>
+        <v>475047</v>
+      </c>
+      <c r="F36" t="n">
+        <v>200869</v>
+      </c>
+      <c r="G36" t="n">
+        <v>42.28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8.57</v>
+        <v>213.67</v>
       </c>
       <c r="C37" t="n">
-        <v>848793</v>
+        <v>213.67</v>
       </c>
       <c r="D37" t="n">
-        <v>470154</v>
+        <v>213.67</v>
       </c>
       <c r="E37" t="n">
-        <v>55.39</v>
+        <v>469353</v>
+      </c>
+      <c r="F37" t="n">
+        <v>135879</v>
+      </c>
+      <c r="G37" t="n">
+        <v>28.95</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>9.42</v>
+        <v>216.38</v>
       </c>
       <c r="C38" t="n">
-        <v>2865353</v>
+        <v>216.38</v>
       </c>
       <c r="D38" t="n">
-        <v>1833547</v>
+        <v>216.38</v>
       </c>
       <c r="E38" t="n">
-        <v>63.99</v>
+        <v>187584</v>
+      </c>
+      <c r="F38" t="n">
+        <v>79614</v>
+      </c>
+      <c r="G38" t="n">
+        <v>42.44</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10.36</v>
+        <v>215.25</v>
       </c>
       <c r="C39" t="n">
-        <v>3144533</v>
+        <v>215.25</v>
       </c>
       <c r="D39" t="n">
-        <v>1949357</v>
+        <v>215.25</v>
       </c>
       <c r="E39" t="n">
-        <v>61.99</v>
+        <v>274412</v>
+      </c>
+      <c r="F39" t="n">
+        <v>187382</v>
+      </c>
+      <c r="G39" t="n">
+        <v>68.28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>11.39</v>
+        <v>216.7</v>
       </c>
       <c r="C40" t="n">
-        <v>3861846</v>
+        <v>216.7</v>
       </c>
       <c r="D40" t="n">
-        <v>2252473</v>
+        <v>216.7</v>
       </c>
       <c r="E40" t="n">
-        <v>58.33</v>
+        <v>438478</v>
+      </c>
+      <c r="F40" t="n">
+        <v>327645</v>
+      </c>
+      <c r="G40" t="n">
+        <v>74.72</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10.93</v>
+        <v>216.58</v>
       </c>
       <c r="C41" t="n">
-        <v>6596371</v>
+        <v>216.58</v>
       </c>
       <c r="D41" t="n">
-        <v>3072063</v>
+        <v>216.58</v>
       </c>
       <c r="E41" t="n">
-        <v>46.57</v>
+        <v>203047</v>
+      </c>
+      <c r="F41" t="n">
+        <v>120142</v>
+      </c>
+      <c r="G41" t="n">
+        <v>59.17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10.39</v>
+        <v>214.36</v>
       </c>
       <c r="C42" t="n">
-        <v>2869997</v>
+        <v>214.36</v>
       </c>
       <c r="D42" t="n">
-        <v>1561256</v>
+        <v>214.36</v>
       </c>
       <c r="E42" t="n">
-        <v>54.4</v>
+        <v>390722</v>
+      </c>
+      <c r="F42" t="n">
+        <v>226568</v>
+      </c>
+      <c r="G42" t="n">
+        <v>57.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>9.880000000000001</v>
+        <v>216.69</v>
       </c>
       <c r="C43" t="n">
-        <v>4046133</v>
+        <v>216.69</v>
       </c>
       <c r="D43" t="n">
-        <v>1612495</v>
+        <v>216.69</v>
       </c>
       <c r="E43" t="n">
-        <v>39.85</v>
+        <v>1238619</v>
+      </c>
+      <c r="F43" t="n">
+        <v>844863</v>
+      </c>
+      <c r="G43" t="n">
+        <v>68.20999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>9.98</v>
+        <v>214.79</v>
       </c>
       <c r="C44" t="n">
-        <v>2764538</v>
+        <v>214.79</v>
       </c>
       <c r="D44" t="n">
-        <v>1345752</v>
+        <v>214.79</v>
       </c>
       <c r="E44" t="n">
-        <v>48.68</v>
+        <v>2088319</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1420279</v>
+      </c>
+      <c r="G44" t="n">
+        <v>68.01000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10.1</v>
+        <v>209.05</v>
       </c>
       <c r="C45" t="n">
-        <v>1410824</v>
+        <v>209.05</v>
       </c>
       <c r="D45" t="n">
-        <v>908932</v>
+        <v>209.05</v>
       </c>
       <c r="E45" t="n">
-        <v>64.43000000000001</v>
+        <v>478596</v>
+      </c>
+      <c r="F45" t="n">
+        <v>225842</v>
+      </c>
+      <c r="G45" t="n">
+        <v>47.19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10.6</v>
+        <v>210.15</v>
       </c>
       <c r="C46" t="n">
-        <v>1356146</v>
+        <v>210.15</v>
       </c>
       <c r="D46" t="n">
-        <v>1008266</v>
+        <v>210.15</v>
       </c>
       <c r="E46" t="n">
-        <v>74.34999999999999</v>
+        <v>633602</v>
+      </c>
+      <c r="F46" t="n">
+        <v>290299</v>
+      </c>
+      <c r="G46" t="n">
+        <v>45.82</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10.61</v>
+        <v>206.36</v>
       </c>
       <c r="C47" t="n">
-        <v>3465171</v>
+        <v>206.36</v>
       </c>
       <c r="D47" t="n">
-        <v>1583925</v>
+        <v>206.36</v>
       </c>
       <c r="E47" t="n">
-        <v>45.71</v>
+        <v>1410754</v>
+      </c>
+      <c r="F47" t="n">
+        <v>673039</v>
+      </c>
+      <c r="G47" t="n">
+        <v>47.71</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10.92</v>
+        <v>204.35</v>
       </c>
       <c r="C48" t="n">
-        <v>3989765</v>
+        <v>204.35</v>
       </c>
       <c r="D48" t="n">
-        <v>2321578</v>
+        <v>204.35</v>
       </c>
       <c r="E48" t="n">
-        <v>58.19</v>
+        <v>4158267</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2878112</v>
+      </c>
+      <c r="G48" t="n">
+        <v>69.20999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10.88</v>
+        <v>203.79</v>
       </c>
       <c r="C49" t="n">
-        <v>1741390</v>
+        <v>203.79</v>
       </c>
       <c r="D49" t="n">
-        <v>1203091</v>
+        <v>203.79</v>
       </c>
       <c r="E49" t="n">
-        <v>69.09</v>
+        <v>1435639</v>
+      </c>
+      <c r="F49" t="n">
+        <v>798255</v>
+      </c>
+      <c r="G49" t="n">
+        <v>55.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10.53</v>
+        <v>208.9</v>
       </c>
       <c r="C50" t="n">
-        <v>1114445</v>
+        <v>208.9</v>
       </c>
       <c r="D50" t="n">
-        <v>629389</v>
+        <v>208.9</v>
       </c>
       <c r="E50" t="n">
-        <v>56.48</v>
+        <v>1453199</v>
+      </c>
+      <c r="F50" t="n">
+        <v>886514</v>
+      </c>
+      <c r="G50" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10.26</v>
+        <v>208</v>
       </c>
       <c r="C51" t="n">
-        <v>1001497</v>
+        <v>208</v>
       </c>
       <c r="D51" t="n">
-        <v>576439</v>
+        <v>208</v>
       </c>
       <c r="E51" t="n">
-        <v>57.56</v>
+        <v>829611</v>
+      </c>
+      <c r="F51" t="n">
+        <v>519554</v>
+      </c>
+      <c r="G51" t="n">
+        <v>62.63</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10.32</v>
+        <v>210.14</v>
       </c>
       <c r="C52" t="n">
-        <v>1189539</v>
+        <v>210.14</v>
       </c>
       <c r="D52" t="n">
-        <v>557129</v>
+        <v>210.14</v>
       </c>
       <c r="E52" t="n">
-        <v>46.84</v>
+        <v>1105011</v>
+      </c>
+      <c r="F52" t="n">
+        <v>714863</v>
+      </c>
+      <c r="G52" t="n">
+        <v>64.69</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10.21</v>
+        <v>210.02</v>
       </c>
       <c r="C53" t="n">
-        <v>968749</v>
+        <v>210.02</v>
       </c>
       <c r="D53" t="n">
-        <v>566626</v>
+        <v>210.02</v>
       </c>
       <c r="E53" t="n">
-        <v>58.49</v>
+        <v>1145469</v>
+      </c>
+      <c r="F53" t="n">
+        <v>764295</v>
+      </c>
+      <c r="G53" t="n">
+        <v>66.72</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10.01</v>
+        <v>212.55</v>
       </c>
       <c r="C54" t="n">
-        <v>1091873</v>
+        <v>212.55</v>
       </c>
       <c r="D54" t="n">
-        <v>644783</v>
+        <v>212.55</v>
       </c>
       <c r="E54" t="n">
-        <v>59.05</v>
+        <v>358793</v>
+      </c>
+      <c r="F54" t="n">
+        <v>202445</v>
+      </c>
+      <c r="G54" t="n">
+        <v>56.42</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10.06</v>
+        <v>211.3</v>
       </c>
       <c r="C55" t="n">
-        <v>845266</v>
+        <v>211.3</v>
       </c>
       <c r="D55" t="n">
-        <v>493558</v>
+        <v>211.3</v>
       </c>
       <c r="E55" t="n">
-        <v>58.39</v>
+        <v>486301</v>
+      </c>
+      <c r="F55" t="n">
+        <v>268065</v>
+      </c>
+      <c r="G55" t="n">
+        <v>55.12</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10.56</v>
+        <v>211.43</v>
       </c>
       <c r="C56" t="n">
-        <v>985613</v>
+        <v>211.43</v>
       </c>
       <c r="D56" t="n">
-        <v>738698</v>
+        <v>211.43</v>
       </c>
       <c r="E56" t="n">
-        <v>74.95</v>
+        <v>24157</v>
+      </c>
+      <c r="F56" t="n">
+        <v>13037</v>
+      </c>
+      <c r="G56" t="n">
+        <v>53.97</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10.7</v>
+        <v>210.15</v>
       </c>
       <c r="C57" t="n">
-        <v>3802987</v>
+        <v>210.15</v>
       </c>
       <c r="D57" t="n">
-        <v>1854640</v>
+        <v>210.15</v>
       </c>
       <c r="E57" t="n">
-        <v>48.77</v>
+        <v>453129</v>
+      </c>
+      <c r="F57" t="n">
+        <v>190352</v>
+      </c>
+      <c r="G57" t="n">
+        <v>42.01</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10.77</v>
+        <v>213.02</v>
       </c>
       <c r="C58" t="n">
-        <v>1029880</v>
+        <v>213.02</v>
       </c>
       <c r="D58" t="n">
-        <v>629716</v>
+        <v>213.02</v>
       </c>
       <c r="E58" t="n">
-        <v>61.14</v>
+        <v>924950</v>
+      </c>
+      <c r="F58" t="n">
+        <v>661001</v>
+      </c>
+      <c r="G58" t="n">
+        <v>71.45999999999999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>11.29</v>
+        <v>214.92</v>
       </c>
       <c r="C59" t="n">
-        <v>3673022</v>
+        <v>214.92</v>
       </c>
       <c r="D59" t="n">
-        <v>2714790</v>
+        <v>214.92</v>
       </c>
       <c r="E59" t="n">
-        <v>73.91</v>
+        <v>939743</v>
+      </c>
+      <c r="F59" t="n">
+        <v>641877</v>
+      </c>
+      <c r="G59" t="n">
+        <v>68.3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>11.85</v>
+        <v>211.85</v>
       </c>
       <c r="C60" t="n">
-        <v>1595480</v>
+        <v>211.85</v>
       </c>
       <c r="D60" t="n">
-        <v>1182574</v>
+        <v>211.85</v>
       </c>
       <c r="E60" t="n">
-        <v>74.12</v>
+        <v>273598</v>
+      </c>
+      <c r="F60" t="n">
+        <v>154783</v>
+      </c>
+      <c r="G60" t="n">
+        <v>56.57</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>12.44</v>
+        <v>211.7</v>
       </c>
       <c r="C61" t="n">
-        <v>2843186</v>
+        <v>211.7</v>
       </c>
       <c r="D61" t="n">
-        <v>1596248</v>
+        <v>211.7</v>
       </c>
       <c r="E61" t="n">
-        <v>56.14</v>
+        <v>1216861</v>
+      </c>
+      <c r="F61" t="n">
+        <v>928450</v>
+      </c>
+      <c r="G61" t="n">
+        <v>76.3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>12.97</v>
+        <v>210.55</v>
       </c>
       <c r="C62" t="n">
-        <v>7412454</v>
+        <v>210.55</v>
       </c>
       <c r="D62" t="n">
-        <v>4306631</v>
+        <v>210.55</v>
       </c>
       <c r="E62" t="n">
-        <v>58.1</v>
+        <v>559057</v>
+      </c>
+      <c r="F62" t="n">
+        <v>368637</v>
+      </c>
+      <c r="G62" t="n">
+        <v>65.94</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>13.59</v>
+        <v>209.17</v>
       </c>
       <c r="C63" t="n">
-        <v>6640140</v>
+        <v>209.17</v>
       </c>
       <c r="D63" t="n">
-        <v>4907683</v>
+        <v>209.17</v>
       </c>
       <c r="E63" t="n">
-        <v>73.91</v>
+        <v>1321146</v>
+      </c>
+      <c r="F63" t="n">
+        <v>915729</v>
+      </c>
+      <c r="G63" t="n">
+        <v>69.31</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>12.94</v>
+        <v>206.56</v>
       </c>
       <c r="C64" t="n">
-        <v>12555219</v>
+        <v>206.56</v>
       </c>
       <c r="D64" t="n">
-        <v>4902158</v>
+        <v>206.56</v>
       </c>
       <c r="E64" t="n">
-        <v>39.04</v>
+        <v>924070</v>
+      </c>
+      <c r="F64" t="n">
+        <v>645749</v>
+      </c>
+      <c r="G64" t="n">
+        <v>69.88</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>205.63</v>
+      </c>
+      <c r="C65" t="n">
+        <v>205.63</v>
+      </c>
+      <c r="D65" t="n">
+        <v>205.63</v>
+      </c>
+      <c r="E65" t="n">
+        <v>510129</v>
+      </c>
+      <c r="F65" t="n">
+        <v>296094</v>
+      </c>
+      <c r="G65" t="n">
+        <v>58.04</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>205.63</v>
+      </c>
+      <c r="C66" t="n">
+        <v>205.63</v>
+      </c>
+      <c r="D66" t="n">
+        <v>205.63</v>
+      </c>
+      <c r="E66" t="n">
+        <v>510129</v>
+      </c>
+      <c r="F66" t="n">
+        <v>296094</v>
+      </c>
+      <c r="G66" t="n">
+        <v>58.04</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>203.45</v>
+      </c>
+      <c r="C67" t="n">
+        <v>203.45</v>
+      </c>
+      <c r="D67" t="n">
+        <v>203.45</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1218056</v>
+      </c>
+      <c r="F67" t="n">
+        <v>627608</v>
+      </c>
+      <c r="G67" t="n">
+        <v>51.53</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>205.95</v>
+      </c>
+      <c r="C68" t="n">
+        <v>205.95</v>
+      </c>
+      <c r="D68" t="n">
+        <v>205.95</v>
+      </c>
+      <c r="E68" t="n">
+        <v>590460</v>
+      </c>
+      <c r="F68" t="n">
+        <v>383726</v>
+      </c>
+      <c r="G68" t="n">
+        <v>64.98999999999999</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>205.95</v>
+      </c>
+      <c r="C69" t="n">
+        <v>205.95</v>
+      </c>
+      <c r="D69" t="n">
+        <v>205.95</v>
+      </c>
+      <c r="E69" t="n">
+        <v>590460</v>
+      </c>
+      <c r="F69" t="n">
+        <v>383726</v>
+      </c>
+      <c r="G69" t="n">
+        <v>64.98999999999999</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>209.84</v>
+      </c>
+      <c r="C70" t="n">
+        <v>209.84</v>
+      </c>
+      <c r="D70" t="n">
+        <v>209.84</v>
+      </c>
+      <c r="E70" t="n">
+        <v>439542</v>
+      </c>
+      <c r="F70" t="n">
+        <v>255257</v>
+      </c>
+      <c r="G70" t="n">
+        <v>58.07</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>216.56</v>
+      </c>
+      <c r="C71" t="n">
+        <v>216.56</v>
+      </c>
+      <c r="D71" t="n">
+        <v>216.56</v>
+      </c>
+      <c r="E71" t="n">
+        <v>804580</v>
+      </c>
+      <c r="F71" t="n">
+        <v>430381</v>
+      </c>
+      <c r="G71" t="n">
+        <v>53.49</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>218.95</v>
+      </c>
+      <c r="C72" t="n">
+        <v>218.95</v>
+      </c>
+      <c r="D72" t="n">
+        <v>218.95</v>
+      </c>
+      <c r="E72" t="n">
+        <v>455039</v>
+      </c>
+      <c r="F72" t="n">
+        <v>216547</v>
+      </c>
+      <c r="G72" t="n">
+        <v>47.59</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>212.92</v>
+      </c>
+      <c r="C73" t="n">
+        <v>212.92</v>
+      </c>
+      <c r="D73" t="n">
+        <v>212.92</v>
+      </c>
+      <c r="E73" t="n">
+        <v>467826</v>
+      </c>
+      <c r="F73" t="n">
+        <v>201176</v>
+      </c>
+      <c r="G73" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>215.4</v>
+      </c>
+      <c r="C74" t="n">
+        <v>215.4</v>
+      </c>
+      <c r="D74" t="n">
+        <v>215.4</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2355971</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1635033</v>
+      </c>
+      <c r="G74" t="n">
+        <v>69.40000000000001</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>213.59</v>
+      </c>
+      <c r="C75" t="n">
+        <v>213.59</v>
+      </c>
+      <c r="D75" t="n">
+        <v>213.59</v>
+      </c>
+      <c r="E75" t="n">
+        <v>483914</v>
+      </c>
+      <c r="F75" t="n">
+        <v>257830</v>
+      </c>
+      <c r="G75" t="n">
+        <v>53.28</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>216.99</v>
+      </c>
+      <c r="C76" t="n">
+        <v>216.99</v>
+      </c>
+      <c r="D76" t="n">
+        <v>216.99</v>
+      </c>
+      <c r="E76" t="n">
+        <v>729470</v>
+      </c>
+      <c r="F76" t="n">
+        <v>504564</v>
+      </c>
+      <c r="G76" t="n">
+        <v>69.17</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>225.57</v>
+      </c>
+      <c r="C77" t="n">
+        <v>225.57</v>
+      </c>
+      <c r="D77" t="n">
+        <v>225.57</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1403248</v>
+      </c>
+      <c r="F77" t="n">
+        <v>744402</v>
+      </c>
+      <c r="G77" t="n">
+        <v>53.05</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>229.03</v>
+      </c>
+      <c r="C78" t="n">
+        <v>229.03</v>
+      </c>
+      <c r="D78" t="n">
+        <v>229.03</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1123967</v>
+      </c>
+      <c r="F78" t="n">
+        <v>677645</v>
+      </c>
+      <c r="G78" t="n">
+        <v>60.29</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>227.4</v>
+      </c>
+      <c r="C79" t="n">
+        <v>227.4</v>
+      </c>
+      <c r="D79" t="n">
+        <v>227.4</v>
+      </c>
+      <c r="E79" t="n">
+        <v>886090</v>
+      </c>
+      <c r="F79" t="n">
+        <v>411598</v>
+      </c>
+      <c r="G79" t="n">
+        <v>46.45</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>230.91</v>
+      </c>
+      <c r="C80" t="n">
+        <v>230.91</v>
+      </c>
+      <c r="D80" t="n">
+        <v>230.91</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1258352</v>
+      </c>
+      <c r="F80" t="n">
+        <v>791032</v>
+      </c>
+      <c r="G80" t="n">
+        <v>62.86</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>228.84</v>
+      </c>
+      <c r="C81" t="n">
+        <v>228.84</v>
+      </c>
+      <c r="D81" t="n">
+        <v>228.84</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1243679</v>
+      </c>
+      <c r="F81" t="n">
+        <v>516341</v>
+      </c>
+      <c r="G81" t="n">
+        <v>41.52</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>228.04</v>
+      </c>
+      <c r="C82" t="n">
+        <v>228.04</v>
+      </c>
+      <c r="D82" t="n">
+        <v>228.04</v>
+      </c>
+      <c r="E82" t="n">
+        <v>540395</v>
+      </c>
+      <c r="F82" t="n">
+        <v>356554</v>
+      </c>
+      <c r="G82" t="n">
+        <v>65.98</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>226.29</v>
+      </c>
+      <c r="C83" t="n">
+        <v>226.29</v>
+      </c>
+      <c r="D83" t="n">
+        <v>226.29</v>
+      </c>
+      <c r="E83" t="n">
+        <v>755878</v>
+      </c>
+      <c r="F83" t="n">
+        <v>522376</v>
+      </c>
+      <c r="G83" t="n">
+        <v>69.11</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>230.22</v>
+      </c>
+      <c r="C84" t="n">
+        <v>230.22</v>
+      </c>
+      <c r="D84" t="n">
+        <v>230.22</v>
+      </c>
+      <c r="E84" t="n">
+        <v>900675</v>
+      </c>
+      <c r="F84" t="n">
+        <v>424172</v>
+      </c>
+      <c r="G84" t="n">
+        <v>47.09</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>228.02</v>
+      </c>
+      <c r="C85" t="n">
+        <v>228.02</v>
+      </c>
+      <c r="D85" t="n">
+        <v>228.02</v>
+      </c>
+      <c r="E85" t="n">
+        <v>240437</v>
+      </c>
+      <c r="F85" t="n">
+        <v>129336</v>
+      </c>
+      <c r="G85" t="n">
+        <v>53.79</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>232.1</v>
+      </c>
+      <c r="C86" t="n">
+        <v>232.1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>232.1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>2104523</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1274088</v>
+      </c>
+      <c r="G86" t="n">
+        <v>60.54</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2024-12-16</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>231.08</v>
+      </c>
+      <c r="C87" t="n">
+        <v>231.08</v>
+      </c>
+      <c r="D87" t="n">
+        <v>231.08</v>
+      </c>
+      <c r="E87" t="n">
+        <v>6530069</v>
+      </c>
+      <c r="F87" t="n">
+        <v>2852977</v>
+      </c>
+      <c r="G87" t="n">
+        <v>43.69</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>227.62</v>
+      </c>
+      <c r="C88" t="n">
+        <v>227.62</v>
+      </c>
+      <c r="D88" t="n">
+        <v>227.62</v>
+      </c>
+      <c r="E88" t="n">
+        <v>617635</v>
+      </c>
+      <c r="F88" t="n">
+        <v>307333</v>
+      </c>
+      <c r="G88" t="n">
+        <v>49.76</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>227.04</v>
+      </c>
+      <c r="C89" t="n">
+        <v>227.04</v>
+      </c>
+      <c r="D89" t="n">
+        <v>227.04</v>
+      </c>
+      <c r="E89" t="n">
+        <v>364703</v>
+      </c>
+      <c r="F89" t="n">
+        <v>146194</v>
+      </c>
+      <c r="G89" t="n">
+        <v>40.09</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2024-12-19</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>225.95</v>
+      </c>
+      <c r="C90" t="n">
+        <v>225.95</v>
+      </c>
+      <c r="D90" t="n">
+        <v>225.95</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1142241</v>
+      </c>
+      <c r="F90" t="n">
+        <v>787548</v>
+      </c>
+      <c r="G90" t="n">
+        <v>68.95</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>220.41</v>
+      </c>
+      <c r="C91" t="n">
+        <v>220.41</v>
+      </c>
+      <c r="D91" t="n">
+        <v>220.41</v>
+      </c>
+      <c r="E91" t="n">
+        <v>705858</v>
+      </c>
+      <c r="F91" t="n">
+        <v>371841</v>
+      </c>
+      <c r="G91" t="n">
+        <v>52.68</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2024-12-23</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>221.08</v>
+      </c>
+      <c r="C92" t="n">
+        <v>221.08</v>
+      </c>
+      <c r="D92" t="n">
+        <v>221.08</v>
+      </c>
+      <c r="E92" t="n">
+        <v>301059</v>
+      </c>
+      <c r="F92" t="n">
+        <v>151454</v>
+      </c>
+      <c r="G92" t="n">
+        <v>50.31</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2024-12-24</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>219.02</v>
+      </c>
+      <c r="C93" t="n">
+        <v>219.02</v>
+      </c>
+      <c r="D93" t="n">
+        <v>219.02</v>
+      </c>
+      <c r="E93" t="n">
+        <v>766019</v>
+      </c>
+      <c r="F93" t="n">
+        <v>541554</v>
+      </c>
+      <c r="G93" t="n">
+        <v>70.7</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2024-12-25</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>219.02</v>
+      </c>
+      <c r="C94" t="n">
+        <v>219.02</v>
+      </c>
+      <c r="D94" t="n">
+        <v>219.02</v>
+      </c>
+      <c r="E94" t="n">
+        <v>766019</v>
+      </c>
+      <c r="F94" t="n">
+        <v>541554</v>
+      </c>
+      <c r="G94" t="n">
+        <v>70.7</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2024-12-26</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>220.93</v>
+      </c>
+      <c r="C95" t="n">
+        <v>220.93</v>
+      </c>
+      <c r="D95" t="n">
+        <v>220.93</v>
+      </c>
+      <c r="E95" t="n">
+        <v>401497</v>
+      </c>
+      <c r="F95" t="n">
+        <v>230619</v>
+      </c>
+      <c r="G95" t="n">
+        <v>57.44</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>220.16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>220.16</v>
+      </c>
+      <c r="D96" t="n">
+        <v>220.16</v>
+      </c>
+      <c r="E96" t="n">
+        <v>235710</v>
+      </c>
+      <c r="F96" t="n">
+        <v>135580</v>
+      </c>
+      <c r="G96" t="n">
+        <v>57.52</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>219.17</v>
+      </c>
+      <c r="C97" t="n">
+        <v>219.17</v>
+      </c>
+      <c r="D97" t="n">
+        <v>219.17</v>
+      </c>
+      <c r="E97" t="n">
+        <v>277487</v>
+      </c>
+      <c r="F97" t="n">
+        <v>141111</v>
+      </c>
+      <c r="G97" t="n">
+        <v>50.85</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>217.69</v>
+      </c>
+      <c r="C98" t="n">
+        <v>217.69</v>
+      </c>
+      <c r="D98" t="n">
+        <v>217.69</v>
+      </c>
+      <c r="E98" t="n">
+        <v>2708979</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1688322</v>
+      </c>
+      <c r="G98" t="n">
+        <v>62.32</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>220.11</v>
+      </c>
+      <c r="C99" t="n">
+        <v>220.11</v>
+      </c>
+      <c r="D99" t="n">
+        <v>220.11</v>
+      </c>
+      <c r="E99" t="n">
+        <v>284618</v>
+      </c>
+      <c r="F99" t="n">
+        <v>133175</v>
+      </c>
+      <c r="G99" t="n">
+        <v>46.79</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>227.08</v>
+      </c>
+      <c r="C100" t="n">
+        <v>227.08</v>
+      </c>
+      <c r="D100" t="n">
+        <v>227.08</v>
+      </c>
+      <c r="E100" t="n">
+        <v>553630</v>
+      </c>
+      <c r="F100" t="n">
+        <v>338136</v>
+      </c>
+      <c r="G100" t="n">
+        <v>61.08</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2025-01-03</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>226.16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>226.16</v>
+      </c>
+      <c r="D101" t="n">
+        <v>226.16</v>
+      </c>
+      <c r="E101" t="n">
+        <v>447645</v>
+      </c>
+      <c r="F101" t="n">
+        <v>267214</v>
+      </c>
+      <c r="G101" t="n">
+        <v>59.69</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2025-01-06</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>221.82</v>
+      </c>
+      <c r="C102" t="n">
+        <v>221.82</v>
+      </c>
+      <c r="D102" t="n">
+        <v>221.82</v>
+      </c>
+      <c r="E102" t="n">
+        <v>494143</v>
+      </c>
+      <c r="F102" t="n">
+        <v>200389</v>
+      </c>
+      <c r="G102" t="n">
+        <v>40.55</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2025-01-07</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>223.61</v>
+      </c>
+      <c r="C103" t="n">
+        <v>223.61</v>
+      </c>
+      <c r="D103" t="n">
+        <v>223.61</v>
+      </c>
+      <c r="E103" t="n">
+        <v>263925</v>
+      </c>
+      <c r="F103" t="n">
+        <v>130151</v>
+      </c>
+      <c r="G103" t="n">
+        <v>49.31</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2025-01-08</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>219.77</v>
+      </c>
+      <c r="C104" t="n">
+        <v>219.77</v>
+      </c>
+      <c r="D104" t="n">
+        <v>219.77</v>
+      </c>
+      <c r="E104" t="n">
+        <v>447597</v>
+      </c>
+      <c r="F104" t="n">
+        <v>282776</v>
+      </c>
+      <c r="G104" t="n">
+        <v>63.18</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>217.07</v>
+      </c>
+      <c r="C105" t="n">
+        <v>217.07</v>
+      </c>
+      <c r="D105" t="n">
+        <v>217.07</v>
+      </c>
+      <c r="E105" t="n">
+        <v>194781</v>
+      </c>
+      <c r="F105" t="n">
+        <v>98161</v>
+      </c>
+      <c r="G105" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>209.26</v>
+      </c>
+      <c r="C106" t="n">
+        <v>209.26</v>
+      </c>
+      <c r="D106" t="n">
+        <v>209.26</v>
+      </c>
+      <c r="E106" t="n">
+        <v>440705</v>
+      </c>
+      <c r="F106" t="n">
+        <v>188913</v>
+      </c>
+      <c r="G106" t="n">
+        <v>42.87</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>204.52</v>
+      </c>
+      <c r="C107" t="n">
+        <v>204.52</v>
+      </c>
+      <c r="D107" t="n">
+        <v>204.52</v>
+      </c>
+      <c r="E107" t="n">
+        <v>408661</v>
+      </c>
+      <c r="F107" t="n">
+        <v>241486</v>
+      </c>
+      <c r="G107" t="n">
+        <v>59.09</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>202.26</v>
+      </c>
+      <c r="C108" t="n">
+        <v>202.26</v>
+      </c>
+      <c r="D108" t="n">
+        <v>202.26</v>
+      </c>
+      <c r="E108" t="n">
+        <v>569459</v>
+      </c>
+      <c r="F108" t="n">
+        <v>268351</v>
+      </c>
+      <c r="G108" t="n">
+        <v>47.12</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>202.67</v>
+      </c>
+      <c r="C109" t="n">
+        <v>202.67</v>
+      </c>
+      <c r="D109" t="n">
+        <v>202.67</v>
+      </c>
+      <c r="E109" t="n">
+        <v>287362</v>
+      </c>
+      <c r="F109" t="n">
+        <v>120874</v>
+      </c>
+      <c r="G109" t="n">
+        <v>42.06</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2025-01-16</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>204.34</v>
+      </c>
+      <c r="C110" t="n">
+        <v>204.34</v>
+      </c>
+      <c r="D110" t="n">
+        <v>204.34</v>
+      </c>
+      <c r="E110" t="n">
+        <v>872925</v>
+      </c>
+      <c r="F110" t="n">
+        <v>198846</v>
+      </c>
+      <c r="G110" t="n">
+        <v>22.78</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>203.44</v>
+      </c>
+      <c r="C111" t="n">
+        <v>203.44</v>
+      </c>
+      <c r="D111" t="n">
+        <v>203.44</v>
+      </c>
+      <c r="E111" t="n">
+        <v>369557</v>
+      </c>
+      <c r="F111" t="n">
+        <v>165138</v>
+      </c>
+      <c r="G111" t="n">
+        <v>44.69</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>204.51</v>
+      </c>
+      <c r="C112" t="n">
+        <v>204.51</v>
+      </c>
+      <c r="D112" t="n">
+        <v>204.51</v>
+      </c>
+      <c r="E112" t="n">
+        <v>370012</v>
+      </c>
+      <c r="F112" t="n">
+        <v>142643</v>
+      </c>
+      <c r="G112" t="n">
+        <v>38.55</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>205.26</v>
+      </c>
+      <c r="C113" t="n">
+        <v>205.26</v>
+      </c>
+      <c r="D113" t="n">
+        <v>205.26</v>
+      </c>
+      <c r="E113" t="n">
+        <v>421868</v>
+      </c>
+      <c r="F113" t="n">
+        <v>167043</v>
+      </c>
+      <c r="G113" t="n">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>205.37</v>
+      </c>
+      <c r="C114" t="n">
+        <v>205.37</v>
+      </c>
+      <c r="D114" t="n">
+        <v>205.37</v>
+      </c>
+      <c r="E114" t="n">
+        <v>383894</v>
+      </c>
+      <c r="F114" t="n">
+        <v>147150</v>
+      </c>
+      <c r="G114" t="n">
+        <v>38.33</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>218.63</v>
+      </c>
+      <c r="C115" t="n">
+        <v>218.63</v>
+      </c>
+      <c r="D115" t="n">
+        <v>218.63</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1906054</v>
+      </c>
+      <c r="F115" t="n">
+        <v>939795</v>
+      </c>
+      <c r="G115" t="n">
+        <v>49.31</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2025-01-24</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>216.02</v>
+      </c>
+      <c r="C116" t="n">
+        <v>216.02</v>
+      </c>
+      <c r="D116" t="n">
+        <v>216.02</v>
+      </c>
+      <c r="E116" t="n">
+        <v>481066</v>
+      </c>
+      <c r="F116" t="n">
+        <v>210019</v>
+      </c>
+      <c r="G116" t="n">
+        <v>43.66</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2025-01-27</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>214.46</v>
+      </c>
+      <c r="C117" t="n">
+        <v>214.46</v>
+      </c>
+      <c r="D117" t="n">
+        <v>214.46</v>
+      </c>
+      <c r="E117" t="n">
+        <v>417699</v>
+      </c>
+      <c r="F117" t="n">
+        <v>209231</v>
+      </c>
+      <c r="G117" t="n">
+        <v>50.09</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>214.7</v>
+      </c>
+      <c r="C118" t="n">
+        <v>214.7</v>
+      </c>
+      <c r="D118" t="n">
+        <v>214.7</v>
+      </c>
+      <c r="E118" t="n">
+        <v>863548</v>
+      </c>
+      <c r="F118" t="n">
+        <v>427541</v>
+      </c>
+      <c r="G118" t="n">
+        <v>49.51</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>220.24</v>
+      </c>
+      <c r="C119" t="n">
+        <v>220.24</v>
+      </c>
+      <c r="D119" t="n">
+        <v>220.24</v>
+      </c>
+      <c r="E119" t="n">
+        <v>235014</v>
+      </c>
+      <c r="F119" t="n">
+        <v>116958</v>
+      </c>
+      <c r="G119" t="n">
+        <v>49.77</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>219.9</v>
+      </c>
+      <c r="C120" t="n">
+        <v>219.9</v>
+      </c>
+      <c r="D120" t="n">
+        <v>219.9</v>
+      </c>
+      <c r="E120" t="n">
+        <v>156306</v>
+      </c>
+      <c r="F120" t="n">
+        <v>68202</v>
+      </c>
+      <c r="G120" t="n">
+        <v>43.63</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>220.26</v>
+      </c>
+      <c r="C121" t="n">
+        <v>220.26</v>
+      </c>
+      <c r="D121" t="n">
+        <v>220.26</v>
+      </c>
+      <c r="E121" t="n">
+        <v>169690</v>
+      </c>
+      <c r="F121" t="n">
+        <v>93826</v>
+      </c>
+      <c r="G121" t="n">
+        <v>55.29</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>214.28</v>
+      </c>
+      <c r="C122" t="n">
+        <v>214.28</v>
+      </c>
+      <c r="D122" t="n">
+        <v>214.28</v>
+      </c>
+      <c r="E122" t="n">
+        <v>239665</v>
+      </c>
+      <c r="F122" t="n">
+        <v>66941</v>
+      </c>
+      <c r="G122" t="n">
+        <v>27.93</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2025-02-04</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>219.66</v>
+      </c>
+      <c r="C123" t="n">
+        <v>219.66</v>
+      </c>
+      <c r="D123" t="n">
+        <v>219.66</v>
+      </c>
+      <c r="E123" t="n">
+        <v>220640</v>
+      </c>
+      <c r="F123" t="n">
+        <v>76667</v>
+      </c>
+      <c r="G123" t="n">
+        <v>34.75</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>221.02</v>
+      </c>
+      <c r="C124" t="n">
+        <v>221.02</v>
+      </c>
+      <c r="D124" t="n">
+        <v>221.02</v>
+      </c>
+      <c r="E124" t="n">
+        <v>576264</v>
+      </c>
+      <c r="F124" t="n">
+        <v>286527</v>
+      </c>
+      <c r="G124" t="n">
+        <v>49.72</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>219.41</v>
+      </c>
+      <c r="C125" t="n">
+        <v>219.41</v>
+      </c>
+      <c r="D125" t="n">
+        <v>219.41</v>
+      </c>
+      <c r="E125" t="n">
+        <v>149255</v>
+      </c>
+      <c r="F125" t="n">
+        <v>79529</v>
+      </c>
+      <c r="G125" t="n">
+        <v>53.28</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025-02-07</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>221.79</v>
+      </c>
+      <c r="C126" t="n">
+        <v>221.79</v>
+      </c>
+      <c r="D126" t="n">
+        <v>221.79</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1287394</v>
+      </c>
+      <c r="F126" t="n">
+        <v>808669</v>
+      </c>
+      <c r="G126" t="n">
+        <v>62.81</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>220.31</v>
+      </c>
+      <c r="C127" t="n">
+        <v>220.31</v>
+      </c>
+      <c r="D127" t="n">
+        <v>220.31</v>
+      </c>
+      <c r="E127" t="n">
+        <v>451318</v>
+      </c>
+      <c r="F127" t="n">
+        <v>269122</v>
+      </c>
+      <c r="G127" t="n">
+        <v>59.63</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>215.69</v>
+      </c>
+      <c r="C128" t="n">
+        <v>215.69</v>
+      </c>
+      <c r="D128" t="n">
+        <v>215.69</v>
+      </c>
+      <c r="E128" t="n">
+        <v>337222</v>
+      </c>
+      <c r="F128" t="n">
+        <v>152416</v>
+      </c>
+      <c r="G128" t="n">
+        <v>45.2</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>219.28</v>
+      </c>
+      <c r="C129" t="n">
+        <v>219.28</v>
+      </c>
+      <c r="D129" t="n">
+        <v>219.28</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1144993</v>
+      </c>
+      <c r="F129" t="n">
+        <v>508360</v>
+      </c>
+      <c r="G129" t="n">
+        <v>44.4</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>220.12</v>
+      </c>
+      <c r="C130" t="n">
+        <v>220.12</v>
+      </c>
+      <c r="D130" t="n">
+        <v>220.12</v>
+      </c>
+      <c r="E130" t="n">
+        <v>580636</v>
+      </c>
+      <c r="F130" t="n">
+        <v>246060</v>
+      </c>
+      <c r="G130" t="n">
+        <v>42.38</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>214.88</v>
+      </c>
+      <c r="C131" t="n">
+        <v>214.88</v>
+      </c>
+      <c r="D131" t="n">
+        <v>214.88</v>
+      </c>
+      <c r="E131" t="n">
+        <v>257600</v>
+      </c>
+      <c r="F131" t="n">
+        <v>129752</v>
+      </c>
+      <c r="G131" t="n">
+        <v>50.37</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2025-02-17</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>218.79</v>
+      </c>
+      <c r="C132" t="n">
+        <v>218.79</v>
+      </c>
+      <c r="D132" t="n">
+        <v>218.79</v>
+      </c>
+      <c r="E132" t="n">
+        <v>723297</v>
+      </c>
+      <c r="F132" t="n">
+        <v>401154</v>
+      </c>
+      <c r="G132" t="n">
+        <v>55.46</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>216.13</v>
+      </c>
+      <c r="C133" t="n">
+        <v>216.13</v>
+      </c>
+      <c r="D133" t="n">
+        <v>216.13</v>
+      </c>
+      <c r="E133" t="n">
+        <v>427718</v>
+      </c>
+      <c r="F133" t="n">
+        <v>216788</v>
+      </c>
+      <c r="G133" t="n">
+        <v>50.68</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>215.65</v>
+      </c>
+      <c r="C134" t="n">
+        <v>215.65</v>
+      </c>
+      <c r="D134" t="n">
+        <v>215.65</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1539242</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1203857</v>
+      </c>
+      <c r="G134" t="n">
+        <v>78.20999999999999</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>215.07</v>
+      </c>
+      <c r="C135" t="n">
+        <v>215.07</v>
+      </c>
+      <c r="D135" t="n">
+        <v>215.07</v>
+      </c>
+      <c r="E135" t="n">
+        <v>594057</v>
+      </c>
+      <c r="F135" t="n">
+        <v>458528</v>
+      </c>
+      <c r="G135" t="n">
+        <v>77.19</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>212.77</v>
+      </c>
+      <c r="C136" t="n">
+        <v>212.77</v>
+      </c>
+      <c r="D136" t="n">
+        <v>212.77</v>
+      </c>
+      <c r="E136" t="n">
+        <v>412677</v>
+      </c>
+      <c r="F136" t="n">
+        <v>164294</v>
+      </c>
+      <c r="G136" t="n">
+        <v>39.81</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>210.75</v>
+      </c>
+      <c r="C137" t="n">
+        <v>210.75</v>
+      </c>
+      <c r="D137" t="n">
+        <v>210.75</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1226598</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1039460</v>
+      </c>
+      <c r="G137" t="n">
+        <v>84.73999999999999</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>209.29</v>
+      </c>
+      <c r="C138" t="n">
+        <v>209.29</v>
+      </c>
+      <c r="D138" t="n">
+        <v>209.29</v>
+      </c>
+      <c r="E138" t="n">
+        <v>994768</v>
+      </c>
+      <c r="F138" t="n">
+        <v>720397</v>
+      </c>
+      <c r="G138" t="n">
+        <v>72.42</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>201.95</v>
+      </c>
+      <c r="C139" t="n">
+        <v>201.95</v>
+      </c>
+      <c r="D139" t="n">
+        <v>201.95</v>
+      </c>
+      <c r="E139" t="n">
+        <v>4198049</v>
+      </c>
+      <c r="F139" t="n">
+        <v>2413667</v>
+      </c>
+      <c r="G139" t="n">
+        <v>57.49</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>195.66</v>
+      </c>
+      <c r="C140" t="n">
+        <v>195.66</v>
+      </c>
+      <c r="D140" t="n">
+        <v>195.66</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1949745</v>
+      </c>
+      <c r="F140" t="n">
+        <v>923967</v>
+      </c>
+      <c r="G140" t="n">
+        <v>47.39</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>200.2</v>
+      </c>
+      <c r="C141" t="n">
+        <v>200.2</v>
+      </c>
+      <c r="D141" t="n">
+        <v>200.2</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1305059</v>
+      </c>
+      <c r="F141" t="n">
+        <v>636191</v>
+      </c>
+      <c r="G141" t="n">
+        <v>48.75</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>200.36</v>
+      </c>
+      <c r="C142" t="n">
+        <v>200.36</v>
+      </c>
+      <c r="D142" t="n">
+        <v>200.36</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1023059</v>
+      </c>
+      <c r="F142" t="n">
+        <v>596266</v>
+      </c>
+      <c r="G142" t="n">
+        <v>58.28</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>202.35</v>
+      </c>
+      <c r="C143" t="n">
+        <v>202.35</v>
+      </c>
+      <c r="D143" t="n">
+        <v>202.35</v>
+      </c>
+      <c r="E143" t="n">
+        <v>865658</v>
+      </c>
+      <c r="F143" t="n">
+        <v>527522</v>
+      </c>
+      <c r="G143" t="n">
+        <v>60.94</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>204.95</v>
+      </c>
+      <c r="C144" t="n">
+        <v>204.95</v>
+      </c>
+      <c r="D144" t="n">
+        <v>204.95</v>
+      </c>
+      <c r="E144" t="n">
+        <v>1791596</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1407614</v>
+      </c>
+      <c r="G144" t="n">
+        <v>78.56999999999999</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>204.72</v>
+      </c>
+      <c r="C145" t="n">
+        <v>204.72</v>
+      </c>
+      <c r="D145" t="n">
+        <v>204.72</v>
+      </c>
+      <c r="E145" t="n">
+        <v>5764013</v>
+      </c>
+      <c r="F145" t="n">
+        <v>4645890</v>
+      </c>
+      <c r="G145" t="n">
+        <v>80.59999999999999</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="C146" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="D146" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="E146" t="n">
+        <v>3927836</v>
+      </c>
+      <c r="F146" t="n">
+        <v>3927836</v>
+      </c>
+      <c r="G146" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="C147" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="D147" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1058003</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1044969</v>
+      </c>
+      <c r="G147" t="n">
+        <v>98.77</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="C148" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="D148" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="E148" t="n">
+        <v>2589765</v>
+      </c>
+      <c r="F148" t="n">
+        <v>2589765</v>
+      </c>
+      <c r="G148" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="C149" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="D149" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="E149" t="n">
+        <v>29850842</v>
+      </c>
+      <c r="F149" t="n">
+        <v>19289717</v>
+      </c>
+      <c r="G149" t="n">
+        <v>64.62</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="C150" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="D150" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="E150" t="n">
+        <v>2900365</v>
+      </c>
+      <c r="F150" t="n">
+        <v>2900355</v>
+      </c>
+      <c r="G150" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="C151" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="D151" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1282883</v>
+      </c>
+      <c r="F151" t="n">
+        <v>833745</v>
+      </c>
+      <c r="G151" t="n">
+        <v>64.98999999999999</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="C152" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="D152" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="E152" t="n">
+        <v>854483</v>
+      </c>
+      <c r="F152" t="n">
+        <v>677452</v>
+      </c>
+      <c r="G152" t="n">
+        <v>79.28</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="C153" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="D153" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="E153" t="n">
+        <v>640873</v>
+      </c>
+      <c r="F153" t="n">
+        <v>510744</v>
+      </c>
+      <c r="G153" t="n">
+        <v>79.7</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C154" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D154" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E154" t="n">
+        <v>562879</v>
+      </c>
+      <c r="F154" t="n">
+        <v>370846</v>
+      </c>
+      <c r="G154" t="n">
+        <v>65.88</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="C155" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="D155" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="E155" t="n">
+        <v>3354430</v>
+      </c>
+      <c r="F155" t="n">
+        <v>2424630</v>
+      </c>
+      <c r="G155" t="n">
+        <v>72.28</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C156" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D156" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E156" t="n">
+        <v>3214611</v>
+      </c>
+      <c r="F156" t="n">
+        <v>2666441</v>
+      </c>
+      <c r="G156" t="n">
+        <v>82.95</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="C157" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="D157" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="E157" t="n">
+        <v>994218</v>
+      </c>
+      <c r="F157" t="n">
+        <v>679959</v>
+      </c>
+      <c r="G157" t="n">
+        <v>68.39</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="C158" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="D158" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1694587</v>
+      </c>
+      <c r="F158" t="n">
+        <v>850596</v>
+      </c>
+      <c r="G158" t="n">
+        <v>50.19</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="C159" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="D159" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="E159" t="n">
+        <v>174018</v>
+      </c>
+      <c r="F159" t="n">
+        <v>174018</v>
+      </c>
+      <c r="G159" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="C160" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="D160" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="E160" t="n">
+        <v>148979</v>
+      </c>
+      <c r="F160" t="n">
+        <v>148979</v>
+      </c>
+      <c r="G160" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="C161" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="D161" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="E161" t="n">
+        <v>8266394</v>
+      </c>
+      <c r="F161" t="n">
+        <v>4237668</v>
+      </c>
+      <c r="G161" t="n">
+        <v>51.26</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="C162" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="D162" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="E162" t="n">
+        <v>2052266</v>
+      </c>
+      <c r="F162" t="n">
+        <v>1203535</v>
+      </c>
+      <c r="G162" t="n">
+        <v>58.64</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>6</v>
+      </c>
+      <c r="C163" t="n">
+        <v>6</v>
+      </c>
+      <c r="D163" t="n">
+        <v>6</v>
+      </c>
+      <c r="E163" t="n">
+        <v>3593221</v>
+      </c>
+      <c r="F163" t="n">
+        <v>2827552</v>
+      </c>
+      <c r="G163" t="n">
+        <v>78.69</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="C164" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="D164" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="E164" t="n">
+        <v>1760511</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1171972</v>
+      </c>
+      <c r="G164" t="n">
+        <v>66.56999999999999</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="C165" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="D165" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="E165" t="n">
+        <v>923681</v>
+      </c>
+      <c r="F165" t="n">
+        <v>589807</v>
+      </c>
+      <c r="G165" t="n">
+        <v>63.85</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="C166" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="D166" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="E166" t="n">
+        <v>2572711</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1371550</v>
+      </c>
+      <c r="G166" t="n">
+        <v>53.31</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="C167" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="D167" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="E167" t="n">
+        <v>776536</v>
+      </c>
+      <c r="F167" t="n">
+        <v>461347</v>
+      </c>
+      <c r="G167" t="n">
+        <v>59.41</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="C168" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="D168" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="E168" t="n">
+        <v>632946</v>
+      </c>
+      <c r="F168" t="n">
+        <v>381273</v>
+      </c>
+      <c r="G168" t="n">
+        <v>60.24</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="C169" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="D169" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="E169" t="n">
+        <v>2330161</v>
+      </c>
+      <c r="F169" t="n">
+        <v>1685995</v>
+      </c>
+      <c r="G169" t="n">
+        <v>72.36</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="C170" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="D170" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1586272</v>
+      </c>
+      <c r="F170" t="n">
+        <v>950650</v>
+      </c>
+      <c r="G170" t="n">
+        <v>59.93</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="C171" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="D171" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="E171" t="n">
+        <v>845993</v>
+      </c>
+      <c r="F171" t="n">
+        <v>468271</v>
+      </c>
+      <c r="G171" t="n">
+        <v>55.35</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="C172" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="D172" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="E172" t="n">
+        <v>885012</v>
+      </c>
+      <c r="F172" t="n">
+        <v>540958</v>
+      </c>
+      <c r="G172" t="n">
+        <v>61.12</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C173" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D173" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E173" t="n">
+        <v>1152845</v>
+      </c>
+      <c r="F173" t="n">
+        <v>688634</v>
+      </c>
+      <c r="G173" t="n">
+        <v>59.73</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="C174" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="D174" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="E174" t="n">
+        <v>955102</v>
+      </c>
+      <c r="F174" t="n">
+        <v>546255</v>
+      </c>
+      <c r="G174" t="n">
+        <v>57.19</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="C175" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="D175" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1670723</v>
+      </c>
+      <c r="F175" t="n">
+        <v>956928</v>
+      </c>
+      <c r="G175" t="n">
+        <v>57.28</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="C176" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="D176" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1423123</v>
+      </c>
+      <c r="F176" t="n">
+        <v>876477</v>
+      </c>
+      <c r="G176" t="n">
+        <v>61.59</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="C177" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="D177" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="E177" t="n">
+        <v>1245350</v>
+      </c>
+      <c r="F177" t="n">
+        <v>632583</v>
+      </c>
+      <c r="G177" t="n">
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="C178" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="D178" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="E178" t="n">
+        <v>951189</v>
+      </c>
+      <c r="F178" t="n">
+        <v>597139</v>
+      </c>
+      <c r="G178" t="n">
+        <v>62.78</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="C179" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="D179" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="E179" t="n">
+        <v>996473</v>
+      </c>
+      <c r="F179" t="n">
+        <v>628812</v>
+      </c>
+      <c r="G179" t="n">
+        <v>63.1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="C180" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="D180" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="E180" t="n">
+        <v>518300</v>
+      </c>
+      <c r="F180" t="n">
+        <v>357823</v>
+      </c>
+      <c r="G180" t="n">
+        <v>69.04000000000001</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C181" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D181" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E181" t="n">
+        <v>414601</v>
+      </c>
+      <c r="F181" t="n">
+        <v>295950</v>
+      </c>
+      <c r="G181" t="n">
+        <v>71.38</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C182" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D182" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E182" t="n">
+        <v>715476</v>
+      </c>
+      <c r="F182" t="n">
+        <v>485366</v>
+      </c>
+      <c r="G182" t="n">
+        <v>67.84</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="C183" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="D183" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="E183" t="n">
+        <v>478788</v>
+      </c>
+      <c r="F183" t="n">
+        <v>334299</v>
+      </c>
+      <c r="G183" t="n">
+        <v>69.81999999999999</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C184" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D184" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E184" t="n">
+        <v>848573</v>
+      </c>
+      <c r="F184" t="n">
+        <v>482644</v>
+      </c>
+      <c r="G184" t="n">
+        <v>56.88</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="C185" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="D185" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="E185" t="n">
+        <v>867235</v>
+      </c>
+      <c r="F185" t="n">
+        <v>670678</v>
+      </c>
+      <c r="G185" t="n">
+        <v>77.34</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C186" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D186" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E186" t="n">
+        <v>844129</v>
+      </c>
+      <c r="F186" t="n">
+        <v>543995</v>
+      </c>
+      <c r="G186" t="n">
+        <v>64.44</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="C187" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="D187" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="E187" t="n">
+        <v>765182</v>
+      </c>
+      <c r="F187" t="n">
+        <v>517440</v>
+      </c>
+      <c r="G187" t="n">
+        <v>67.62</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="D188" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="E188" t="n">
+        <v>372669</v>
+      </c>
+      <c r="F188" t="n">
+        <v>239424</v>
+      </c>
+      <c r="G188" t="n">
+        <v>64.25</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="C189" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="D189" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="E189" t="n">
+        <v>876500</v>
+      </c>
+      <c r="F189" t="n">
+        <v>753454</v>
+      </c>
+      <c r="G189" t="n">
+        <v>85.95999999999999</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="D190" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="E190" t="n">
+        <v>687607</v>
+      </c>
+      <c r="F190" t="n">
+        <v>560861</v>
+      </c>
+      <c r="G190" t="n">
+        <v>81.56999999999999</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C191" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D191" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E191" t="n">
+        <v>575953</v>
+      </c>
+      <c r="F191" t="n">
+        <v>403280</v>
+      </c>
+      <c r="G191" t="n">
+        <v>70.02</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="C192" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="D192" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="E192" t="n">
+        <v>549930</v>
+      </c>
+      <c r="F192" t="n">
+        <v>378261</v>
+      </c>
+      <c r="G192" t="n">
+        <v>68.78</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="C193" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="D193" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="E193" t="n">
+        <v>851170</v>
+      </c>
+      <c r="F193" t="n">
+        <v>584958</v>
+      </c>
+      <c r="G193" t="n">
+        <v>68.72</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="C194" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="D194" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="E194" t="n">
+        <v>334425</v>
+      </c>
+      <c r="F194" t="n">
+        <v>254436</v>
+      </c>
+      <c r="G194" t="n">
+        <v>76.08</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="C195" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="D195" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="E195" t="n">
+        <v>515753</v>
+      </c>
+      <c r="F195" t="n">
+        <v>324387</v>
+      </c>
+      <c r="G195" t="n">
+        <v>62.9</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="C196" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="D196" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="E196" t="n">
+        <v>717814</v>
+      </c>
+      <c r="F196" t="n">
+        <v>498709</v>
+      </c>
+      <c r="G196" t="n">
+        <v>69.48</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>5</v>
+      </c>
+      <c r="C197" t="n">
+        <v>5</v>
+      </c>
+      <c r="D197" t="n">
+        <v>5</v>
+      </c>
+      <c r="E197" t="n">
+        <v>505067</v>
+      </c>
+      <c r="F197" t="n">
+        <v>375941</v>
+      </c>
+      <c r="G197" t="n">
+        <v>74.43000000000001</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="C198" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="D198" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="E198" t="n">
+        <v>558714</v>
+      </c>
+      <c r="F198" t="n">
+        <v>395397</v>
+      </c>
+      <c r="G198" t="n">
+        <v>70.77</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="C199" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="D199" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="E199" t="n">
+        <v>474312</v>
+      </c>
+      <c r="F199" t="n">
+        <v>376199</v>
+      </c>
+      <c r="G199" t="n">
+        <v>79.31</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="C200" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="D200" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="E200" t="n">
+        <v>585617</v>
+      </c>
+      <c r="F200" t="n">
+        <v>353238</v>
+      </c>
+      <c r="G200" t="n">
+        <v>60.32</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="C201" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="D201" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="E201" t="n">
+        <v>1116479</v>
+      </c>
+      <c r="F201" t="n">
+        <v>852650</v>
+      </c>
+      <c r="G201" t="n">
+        <v>76.37</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="C202" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D202" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E202" t="n">
+        <v>6680188</v>
+      </c>
+      <c r="F202" t="n">
+        <v>3446692</v>
+      </c>
+      <c r="G202" t="n">
+        <v>51.6</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="C203" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="D203" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="E203" t="n">
+        <v>940780</v>
+      </c>
+      <c r="F203" t="n">
+        <v>655323</v>
+      </c>
+      <c r="G203" t="n">
+        <v>69.66</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="C204" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="D204" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="E204" t="n">
+        <v>796020</v>
+      </c>
+      <c r="F204" t="n">
+        <v>419572</v>
+      </c>
+      <c r="G204" t="n">
+        <v>52.71</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="C205" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="D205" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="E205" t="n">
+        <v>431146</v>
+      </c>
+      <c r="F205" t="n">
+        <v>268399</v>
+      </c>
+      <c r="G205" t="n">
+        <v>62.25</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="C206" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="D206" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="E206" t="n">
+        <v>775798</v>
+      </c>
+      <c r="F206" t="n">
+        <v>400084</v>
+      </c>
+      <c r="G206" t="n">
+        <v>51.57</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="C207" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="D207" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="E207" t="n">
+        <v>3152788</v>
+      </c>
+      <c r="F207" t="n">
+        <v>1292585</v>
+      </c>
+      <c r="G207" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="C208" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="D208" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="E208" t="n">
+        <v>2403923</v>
+      </c>
+      <c r="F208" t="n">
+        <v>1421706</v>
+      </c>
+      <c r="G208" t="n">
+        <v>59.14</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="C209" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D209" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E209" t="n">
+        <v>650061</v>
+      </c>
+      <c r="F209" t="n">
+        <v>436274</v>
+      </c>
+      <c r="G209" t="n">
+        <v>67.11</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="C210" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="D210" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="E210" t="n">
+        <v>410522</v>
+      </c>
+      <c r="F210" t="n">
+        <v>301427</v>
+      </c>
+      <c r="G210" t="n">
+        <v>73.43000000000001</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="C211" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="D211" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1265186</v>
+      </c>
+      <c r="F211" t="n">
+        <v>943476</v>
+      </c>
+      <c r="G211" t="n">
+        <v>74.56999999999999</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="C212" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="D212" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="E212" t="n">
+        <v>27546759</v>
+      </c>
+      <c r="F212" t="n">
+        <v>17622370</v>
+      </c>
+      <c r="G212" t="n">
+        <v>63.97</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="C213" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="D213" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="E213" t="n">
+        <v>23271133</v>
+      </c>
+      <c r="F213" t="n">
+        <v>10720183</v>
+      </c>
+      <c r="G213" t="n">
+        <v>46.07</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="C214" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="D214" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="E214" t="n">
+        <v>33227088</v>
+      </c>
+      <c r="F214" t="n">
+        <v>13115294</v>
+      </c>
+      <c r="G214" t="n">
+        <v>39.47</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="C215" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="D215" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="E215" t="n">
+        <v>17988293</v>
+      </c>
+      <c r="F215" t="n">
+        <v>6384582</v>
+      </c>
+      <c r="G215" t="n">
+        <v>35.49</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="C216" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D216" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E216" t="n">
+        <v>6419042</v>
+      </c>
+      <c r="F216" t="n">
+        <v>3405087</v>
+      </c>
+      <c r="G216" t="n">
+        <v>53.05</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="C217" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="D217" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="E217" t="n">
+        <v>1241894</v>
+      </c>
+      <c r="F217" t="n">
+        <v>763984</v>
+      </c>
+      <c r="G217" t="n">
+        <v>61.52</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="C218" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="D218" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="E218" t="n">
+        <v>1297041</v>
+      </c>
+      <c r="F218" t="n">
+        <v>885426</v>
+      </c>
+      <c r="G218" t="n">
+        <v>68.27</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="C219" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="D219" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E219" t="n">
+        <v>2443810</v>
+      </c>
+      <c r="F219" t="n">
+        <v>1548415</v>
+      </c>
+      <c r="G219" t="n">
+        <v>63.36</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="C220" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="D220" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E220" t="n">
+        <v>2443810</v>
+      </c>
+      <c r="F220" t="n">
+        <v>1548415</v>
+      </c>
+      <c r="G220" t="n">
+        <v>63.36</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="C221" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="D221" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="E221" t="n">
+        <v>1538645</v>
+      </c>
+      <c r="F221" t="n">
+        <v>1178198</v>
+      </c>
+      <c r="G221" t="n">
+        <v>76.56999999999999</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="C222" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="D222" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="E222" t="n">
+        <v>1694201</v>
+      </c>
+      <c r="F222" t="n">
+        <v>1117022</v>
+      </c>
+      <c r="G222" t="n">
+        <v>65.93000000000001</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="C223" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="D223" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="E223" t="n">
+        <v>1015707</v>
+      </c>
+      <c r="F223" t="n">
+        <v>624448</v>
+      </c>
+      <c r="G223" t="n">
+        <v>61.48</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="C224" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="D224" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="E224" t="n">
+        <v>848793</v>
+      </c>
+      <c r="F224" t="n">
+        <v>470154</v>
+      </c>
+      <c r="G224" t="n">
+        <v>55.39</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="C225" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="D225" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="E225" t="n">
+        <v>2865353</v>
+      </c>
+      <c r="F225" t="n">
+        <v>1833547</v>
+      </c>
+      <c r="G225" t="n">
+        <v>63.99</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="C226" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="D226" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="E226" t="n">
+        <v>3144533</v>
+      </c>
+      <c r="F226" t="n">
+        <v>1949357</v>
+      </c>
+      <c r="G226" t="n">
+        <v>61.99</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="C227" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="D227" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="E227" t="n">
+        <v>3861846</v>
+      </c>
+      <c r="F227" t="n">
+        <v>2252473</v>
+      </c>
+      <c r="G227" t="n">
+        <v>58.33</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="C228" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="D228" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="E228" t="n">
+        <v>6596371</v>
+      </c>
+      <c r="F228" t="n">
+        <v>3072063</v>
+      </c>
+      <c r="G228" t="n">
+        <v>46.57</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="C229" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="D229" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="E229" t="n">
+        <v>2869997</v>
+      </c>
+      <c r="F229" t="n">
+        <v>1561256</v>
+      </c>
+      <c r="G229" t="n">
+        <v>54.4</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="C230" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="D230" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="E230" t="n">
+        <v>4046133</v>
+      </c>
+      <c r="F230" t="n">
+        <v>1612495</v>
+      </c>
+      <c r="G230" t="n">
+        <v>39.85</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="C231" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="D231" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="E231" t="n">
+        <v>2764538</v>
+      </c>
+      <c r="F231" t="n">
+        <v>1345752</v>
+      </c>
+      <c r="G231" t="n">
+        <v>48.68</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="C232" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="D232" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E232" t="n">
+        <v>1410824</v>
+      </c>
+      <c r="F232" t="n">
+        <v>908932</v>
+      </c>
+      <c r="G232" t="n">
+        <v>64.43000000000001</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="C233" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D233" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="E233" t="n">
+        <v>1356146</v>
+      </c>
+      <c r="F233" t="n">
+        <v>1008266</v>
+      </c>
+      <c r="G233" t="n">
+        <v>74.34999999999999</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="C234" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="D234" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="E234" t="n">
+        <v>3465171</v>
+      </c>
+      <c r="F234" t="n">
+        <v>1583925</v>
+      </c>
+      <c r="G234" t="n">
+        <v>45.71</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="C235" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="D235" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="E235" t="n">
+        <v>3989765</v>
+      </c>
+      <c r="F235" t="n">
+        <v>2321578</v>
+      </c>
+      <c r="G235" t="n">
+        <v>58.19</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="C236" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="D236" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="E236" t="n">
+        <v>1741390</v>
+      </c>
+      <c r="F236" t="n">
+        <v>1203091</v>
+      </c>
+      <c r="G236" t="n">
+        <v>69.09</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="C237" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="D237" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="E237" t="n">
+        <v>1114445</v>
+      </c>
+      <c r="F237" t="n">
+        <v>629389</v>
+      </c>
+      <c r="G237" t="n">
+        <v>56.48</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="C238" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="D238" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="E238" t="n">
+        <v>1001497</v>
+      </c>
+      <c r="F238" t="n">
+        <v>576439</v>
+      </c>
+      <c r="G238" t="n">
+        <v>57.56</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="C239" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="D239" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="E239" t="n">
+        <v>1189539</v>
+      </c>
+      <c r="F239" t="n">
+        <v>557129</v>
+      </c>
+      <c r="G239" t="n">
+        <v>46.84</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="C240" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="D240" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="E240" t="n">
+        <v>968749</v>
+      </c>
+      <c r="F240" t="n">
+        <v>566626</v>
+      </c>
+      <c r="G240" t="n">
+        <v>58.49</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="C241" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="D241" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="E241" t="n">
+        <v>1091873</v>
+      </c>
+      <c r="F241" t="n">
+        <v>644783</v>
+      </c>
+      <c r="G241" t="n">
+        <v>59.05</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="C242" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="D242" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="E242" t="n">
+        <v>845266</v>
+      </c>
+      <c r="F242" t="n">
+        <v>493558</v>
+      </c>
+      <c r="G242" t="n">
+        <v>58.39</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="C243" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="D243" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="E243" t="n">
+        <v>985613</v>
+      </c>
+      <c r="F243" t="n">
+        <v>738698</v>
+      </c>
+      <c r="G243" t="n">
+        <v>74.95</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="C244" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="D244" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="E244" t="n">
+        <v>3802987</v>
+      </c>
+      <c r="F244" t="n">
+        <v>1854640</v>
+      </c>
+      <c r="G244" t="n">
+        <v>48.77</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="C245" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="D245" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="E245" t="n">
+        <v>1029880</v>
+      </c>
+      <c r="F245" t="n">
+        <v>629716</v>
+      </c>
+      <c r="G245" t="n">
+        <v>61.14</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="C246" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="D246" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="E246" t="n">
+        <v>3673022</v>
+      </c>
+      <c r="F246" t="n">
+        <v>2714790</v>
+      </c>
+      <c r="G246" t="n">
+        <v>73.91</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="C247" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="D247" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="E247" t="n">
+        <v>1595480</v>
+      </c>
+      <c r="F247" t="n">
+        <v>1182574</v>
+      </c>
+      <c r="G247" t="n">
+        <v>74.12</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="C248" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="D248" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="E248" t="n">
+        <v>2843186</v>
+      </c>
+      <c r="F248" t="n">
+        <v>1596248</v>
+      </c>
+      <c r="G248" t="n">
+        <v>56.14</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="C249" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="D249" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="E249" t="n">
+        <v>7412454</v>
+      </c>
+      <c r="F249" t="n">
+        <v>4306631</v>
+      </c>
+      <c r="G249" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="C250" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="D250" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="E250" t="n">
+        <v>6640140</v>
+      </c>
+      <c r="F250" t="n">
+        <v>4907683</v>
+      </c>
+      <c r="G250" t="n">
+        <v>73.91</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="C251" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="D251" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="E251" t="n">
+        <v>12555219</v>
+      </c>
+      <c r="F251" t="n">
+        <v>4902158</v>
+      </c>
+      <c r="G251" t="n">
+        <v>39.04</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="B65" t="n">
+      <c r="B252" t="n">
         <v>12.3</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C252" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="D252" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E252" t="n">
         <v>7477517</v>
       </c>
-      <c r="D65" t="n">
+      <c r="F252" t="n">
         <v>3511380</v>
       </c>
-      <c r="E65" t="n">
+      <c r="G252" t="n">
         <v>46.96</v>
       </c>
     </row>
